--- a/data/trans_camb/P1410-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1410-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,4</t>
+          <t>-2,68; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,06</t>
+          <t>-1,88; 2,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,6</t>
+          <t>-0,45; 3,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,79</t>
+          <t>-2,07; 2,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,62</t>
+          <t>-0,57; 4,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,9</t>
+          <t>-1,16; 2,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,44</t>
+          <t>-1,73; 1,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,84</t>
+          <t>-0,6; 2,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,65</t>
+          <t>-0,17; 2,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 48,34</t>
+          <t>-51,65; 46,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 62,64</t>
+          <t>-37,65; 76,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 108,55</t>
+          <t>-10,41; 120,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 85,97</t>
+          <t>-37,64; 72,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 137,03</t>
+          <t>-13,45; 130,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 91,2</t>
+          <t>-22,04; 92,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 43,11</t>
+          <t>-34,66; 35,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 81,68</t>
+          <t>-13,32; 73,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 75,1</t>
+          <t>-3,88; 80,47</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,34</t>
+          <t>-2,25; 1,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,37</t>
+          <t>-2,24; 1,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,3</t>
+          <t>-1,63; 2,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,17</t>
+          <t>-1,34; 2,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,15</t>
+          <t>-2,12; 1,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,15</t>
+          <t>-1,21; 2,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,29</t>
+          <t>-1,37; 1,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,75</t>
+          <t>-1,7; 0,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,21</t>
+          <t>-0,72; 1,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-14,69%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-1,97%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 39,56</t>
+          <t>-42,16; 38,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 43,29</t>
+          <t>-42,37; 40,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,54; 35,79</t>
+          <t>-29,59; 60,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 73,49</t>
+          <t>-28,86; 84,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 38,52</t>
+          <t>-45,25; 45,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 75,21</t>
+          <t>-23,52; 72,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 38,01</t>
+          <t>-28,57; 36,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 22,59</t>
+          <t>-35,96; 23,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 33,74</t>
+          <t>-15,1; 44,83</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,54</t>
+          <t>-4,07; 0,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,93</t>
+          <t>-3,82; 0,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,92</t>
+          <t>-1,84; 3,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,19</t>
+          <t>-4,12; 0,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,25</t>
+          <t>-2,44; 2,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,36</t>
+          <t>-3,21; 0,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,44</t>
+          <t>-3,24; -0,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,76</t>
+          <t>-2,48; 0,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,77</t>
+          <t>-2,0; 1,2</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-44,06%</t>
+          <t>-26,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,18%</t>
+          <t>-6,02%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 15,85</t>
+          <t>-61,35; 10,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 27,48</t>
+          <t>-57,75; 14,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 104,24</t>
+          <t>-28,88; 74,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,7; 7,83</t>
+          <t>-68,24; 7,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 66,9</t>
+          <t>-39,93; 60,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,18; -11,15</t>
+          <t>-53,06; 17,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,83; -9,29</t>
+          <t>-55,84; -8,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,76; 19,69</t>
+          <t>-43,11; 13,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 15,91</t>
+          <t>-33,86; 29,04</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,65</t>
+          <t>-2,16; 1,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,07</t>
+          <t>-3,28; 0,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,0</t>
+          <t>-0,82; 2,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,85</t>
+          <t>0,48; 3,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,47</t>
+          <t>0,17; 3,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,0</t>
+          <t>0,42; 3,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,34</t>
+          <t>-0,25; 2,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,35</t>
+          <t>-0,99; 1,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,43</t>
+          <t>0,32; 2,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 42,48</t>
+          <t>-38,04; 44,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,75; 3,27</t>
+          <t>-58,5; 6,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 76,32</t>
+          <t>-16,44; 74,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,21; 194,16</t>
+          <t>13,78; 181,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 164,25</t>
+          <t>2,46; 176,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 155,26</t>
+          <t>8,08; 159,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 74,61</t>
+          <t>-6,32; 72,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 43,62</t>
+          <t>-24,02; 44,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 77,95</t>
+          <t>7,52; 79,96</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,22</t>
+          <t>-1,7; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,05</t>
+          <t>-1,76; 0,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,6</t>
+          <t>-0,22; 1,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,36</t>
+          <t>-0,6; 1,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,86</t>
+          <t>-0,32; 1,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,17</t>
+          <t>-0,25; 1,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,58</t>
+          <t>-0,84; 0,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,63</t>
+          <t>-0,7; 0,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,13</t>
+          <t>0,03; 1,36</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 5,29</t>
+          <t>-34,05; 5,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 1,3</t>
+          <t>-34,56; 2,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 37,82</t>
+          <t>-4,27; 43,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 42,19</t>
+          <t>-13,34; 37,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 56,14</t>
+          <t>-7,43; 54,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 34,53</t>
+          <t>-5,85; 44,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 15,17</t>
+          <t>-18,95; 14,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 16,44</t>
+          <t>-15,57; 16,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 29,43</t>
+          <t>0,57; 36,01</t>
         </is>
       </c>
     </row>
